--- a/output/MACRO-VISA-transactions.xlsx
+++ b/output/MACRO-VISA-transactions.xlsx
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>765962 OF</t>
+          <t>765962 OF USD 11,30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
